--- a/output/Tables/7000 steps/HIA_age_7000steps_1000replicate.xlsx
+++ b/output/Tables/7000 steps/HIA_age_7000steps_1000replicate.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>1089.666</v>
+        <v>1089.681</v>
       </c>
       <c r="D2">
-        <v>1010.299</v>
+        <v>1010.523</v>
       </c>
       <c r="E2">
-        <v>1168.748</v>
+        <v>1168.891</v>
       </c>
       <c r="F2">
-        <v>62166.278</v>
+        <v>62167.64</v>
       </c>
       <c r="G2">
-        <v>57707.626</v>
+        <v>57713.077</v>
       </c>
       <c r="H2">
-        <v>66633.452</v>
+        <v>66644.227</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>8267987835.835</v>
+        <v>8268457035.931</v>
       </c>
       <c r="M2">
-        <v>7672841787.82</v>
+        <v>7673525254.104</v>
       </c>
       <c r="N2">
-        <v>8861926109.912001</v>
+        <v>8861519251.393</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>2385.152</v>
+        <v>2384.956</v>
       </c>
       <c r="D3">
-        <v>2233.053</v>
+        <v>2232.76</v>
       </c>
       <c r="E3">
-        <v>2536.328</v>
+        <v>2535.936</v>
       </c>
       <c r="F3">
-        <v>109958.62</v>
+        <v>109950.056</v>
       </c>
       <c r="G3">
-        <v>103252.969</v>
+        <v>103258.943</v>
       </c>
       <c r="H3">
-        <v>116652.552</v>
+        <v>116629.578</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>14622895971.433</v>
+        <v>14622036742.042</v>
       </c>
       <c r="M3">
-        <v>13731768466.853</v>
+        <v>13730466751.466</v>
       </c>
       <c r="N3">
-        <v>15520044877.034</v>
+        <v>15520374973.852</v>
       </c>
     </row>
     <row r="4">
@@ -534,22 +534,22 @@
         </is>
       </c>
       <c r="C4">
-        <v>7067.403</v>
+        <v>7067.38</v>
       </c>
       <c r="D4">
-        <v>6649.847</v>
+        <v>6648.928</v>
       </c>
       <c r="E4">
-        <v>7482.216</v>
+        <v>7482.965</v>
       </c>
       <c r="F4">
-        <v>258538.749</v>
+        <v>258534.63</v>
       </c>
       <c r="G4">
-        <v>243830.07</v>
+        <v>243814.762</v>
       </c>
       <c r="H4">
-        <v>273245.053</v>
+        <v>273229.975</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>34392661284.767</v>
+        <v>34391483282.894</v>
       </c>
       <c r="M4">
-        <v>32426794895.502</v>
+        <v>32429227877.172</v>
       </c>
       <c r="N4">
-        <v>36364537404.324</v>
+        <v>36362772132.709</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="C5">
-        <v>14320.229</v>
+        <v>14322.771</v>
       </c>
       <c r="D5">
-        <v>13597.684</v>
+        <v>13598.578</v>
       </c>
       <c r="E5">
-        <v>15047.358</v>
+        <v>15049.08</v>
       </c>
       <c r="F5">
-        <v>382108.506</v>
+        <v>382159.404</v>
       </c>
       <c r="G5">
-        <v>363712.751</v>
+        <v>363781.033</v>
       </c>
       <c r="H5">
-        <v>400437.207</v>
+        <v>400524.785</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -609,13 +609,13 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>50820831838.809</v>
+        <v>50830160284.168</v>
       </c>
       <c r="M5">
-        <v>48369367705.422</v>
+        <v>48375753179.612</v>
       </c>
       <c r="N5">
-        <v>53271069523.472</v>
+        <v>53281950089.533</v>
       </c>
     </row>
     <row r="6">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="C6">
-        <v>28291.45</v>
+        <v>28291.527</v>
       </c>
       <c r="D6">
-        <v>26930.767</v>
+        <v>26934.315</v>
       </c>
       <c r="E6">
-        <v>29653.294</v>
+        <v>29651.409</v>
       </c>
       <c r="F6">
-        <v>478374.069</v>
+        <v>478394.419</v>
       </c>
       <c r="G6">
-        <v>456434.268</v>
+        <v>456471.074</v>
       </c>
       <c r="H6">
-        <v>500372.507</v>
+        <v>500416.54</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -657,13 +657,13 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>63625734865.5</v>
+        <v>63626676278.552</v>
       </c>
       <c r="M6">
-        <v>60700382225.319</v>
+        <v>60706807783.388</v>
       </c>
       <c r="N6">
-        <v>66551243613.25</v>
+        <v>66549148389.503</v>
       </c>
     </row>
     <row r="7">
@@ -678,22 +678,22 @@
         </is>
       </c>
       <c r="C7">
-        <v>42658.836</v>
+        <v>42654.439</v>
       </c>
       <c r="D7">
-        <v>40236.202</v>
+        <v>40236.532</v>
       </c>
       <c r="E7">
-        <v>45071.129</v>
+        <v>45071.676</v>
       </c>
       <c r="F7">
-        <v>310705.043</v>
+        <v>310700.772</v>
       </c>
       <c r="G7">
-        <v>295134.076</v>
+        <v>295127.35</v>
       </c>
       <c r="H7">
-        <v>326246.576</v>
+        <v>326242.767</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>41316946523.452</v>
+        <v>41316229515.424</v>
       </c>
       <c r="M7">
-        <v>39262428153.225</v>
+        <v>39255338899.644</v>
       </c>
       <c r="N7">
-        <v>43382591350.528</v>
+        <v>43375802739.703</v>
       </c>
     </row>
     <row r="8">
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="C8">
-        <v>63111.73</v>
+        <v>63115.473</v>
       </c>
       <c r="D8">
-        <v>58098.607</v>
+        <v>58094.457</v>
       </c>
       <c r="E8">
-        <v>68129.322</v>
+        <v>68127.951</v>
       </c>
       <c r="F8">
-        <v>50138.462</v>
+        <v>50151.063</v>
       </c>
       <c r="G8">
-        <v>44515.427</v>
+        <v>44528.198</v>
       </c>
       <c r="H8">
-        <v>55762.718</v>
+        <v>55790.699</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -753,13 +753,13 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>6667158354.591</v>
+        <v>6669183892.697</v>
       </c>
       <c r="M8">
-        <v>5920819157.974</v>
+        <v>5922790174.294</v>
       </c>
       <c r="N8">
-        <v>7415783879.753</v>
+        <v>7417852854.851</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>758.524</v>
+        <v>763.558</v>
       </c>
       <c r="D9">
-        <v>703.369</v>
+        <v>707.972</v>
       </c>
       <c r="E9">
-        <v>814.252</v>
+        <v>819.6369999999999</v>
       </c>
       <c r="F9">
-        <v>2873.6</v>
+        <v>2892.342</v>
       </c>
       <c r="G9">
-        <v>2664.305</v>
+        <v>2680.944</v>
       </c>
       <c r="H9">
-        <v>3086.646</v>
+        <v>3106.485</v>
       </c>
       <c r="I9">
-        <v>42246831.499</v>
+        <v>42522252.144</v>
       </c>
       <c r="J9">
-        <v>39179617.297</v>
+        <v>39433534.431</v>
       </c>
       <c r="K9">
-        <v>45320558.573</v>
+        <v>45631955.659</v>
       </c>
       <c r="L9">
-        <v>382149872.829</v>
+        <v>384638580.13</v>
       </c>
       <c r="M9">
-        <v>354325282.033</v>
+        <v>356508479.633</v>
       </c>
       <c r="N9">
-        <v>410459049.178</v>
+        <v>413222812.784</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>1797.025</v>
+        <v>1805.05</v>
       </c>
       <c r="D10">
-        <v>1686.852</v>
+        <v>1693.908</v>
       </c>
       <c r="E10">
-        <v>1907.321</v>
+        <v>1916.139</v>
       </c>
       <c r="F10">
-        <v>5537.59</v>
+        <v>5561.592</v>
       </c>
       <c r="G10">
-        <v>5202.608</v>
+        <v>5224.788</v>
       </c>
       <c r="H10">
-        <v>5876.55</v>
+        <v>5902.214</v>
       </c>
       <c r="I10">
-        <v>100080082.877</v>
+        <v>100528859.155</v>
       </c>
       <c r="J10">
-        <v>93950060.735</v>
+        <v>94378734.853</v>
       </c>
       <c r="K10">
-        <v>106285885.264</v>
+        <v>106764101.495</v>
       </c>
       <c r="L10">
-        <v>736399401.915</v>
+        <v>739662725.785</v>
       </c>
       <c r="M10">
-        <v>691759944.902</v>
+        <v>694755769.409</v>
       </c>
       <c r="N10">
-        <v>781644642.501</v>
+        <v>785146768.674</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>6899.862</v>
+        <v>6890.468</v>
       </c>
       <c r="D11">
-        <v>6483.741</v>
+        <v>6475.195</v>
       </c>
       <c r="E11">
-        <v>7320.919</v>
+        <v>7308.086</v>
       </c>
       <c r="F11">
-        <v>16983.037</v>
+        <v>16958.899</v>
       </c>
       <c r="G11">
-        <v>15951.459</v>
+        <v>15930.318</v>
       </c>
       <c r="H11">
-        <v>18012.933</v>
+        <v>17987.007</v>
       </c>
       <c r="I11">
-        <v>384312047.775</v>
+        <v>383779268.014</v>
       </c>
       <c r="J11">
-        <v>361234159.077</v>
+        <v>360779321.581</v>
       </c>
       <c r="K11">
-        <v>407760569.757</v>
+        <v>407163523.322</v>
       </c>
       <c r="L11">
-        <v>2258163532.967</v>
+        <v>2255445251.988</v>
       </c>
       <c r="M11">
-        <v>2122288353.699</v>
+        <v>2119206585.63</v>
       </c>
       <c r="N11">
-        <v>2395298071.633</v>
+        <v>2392123627.096</v>
       </c>
     </row>
     <row r="12">
@@ -918,40 +918,40 @@
         </is>
       </c>
       <c r="C12">
-        <v>15320.746</v>
+        <v>15335.848</v>
       </c>
       <c r="D12">
-        <v>14548.861</v>
+        <v>14561.809</v>
       </c>
       <c r="E12">
-        <v>16097.313</v>
+        <v>16114.963</v>
       </c>
       <c r="F12">
-        <v>27481.271</v>
+        <v>27521.334</v>
       </c>
       <c r="G12">
-        <v>26117.628</v>
+        <v>26149.689</v>
       </c>
       <c r="H12">
-        <v>28864.801</v>
+        <v>28914.97</v>
       </c>
       <c r="I12">
-        <v>853475073.444</v>
+        <v>854297678.391</v>
       </c>
       <c r="J12">
-        <v>810321918.72</v>
+        <v>810884247.89</v>
       </c>
       <c r="K12">
-        <v>896592109.2539999</v>
+        <v>897596518.6720001</v>
       </c>
       <c r="L12">
-        <v>3655207872.8</v>
+        <v>3659991611.155</v>
       </c>
       <c r="M12">
-        <v>3473743414.409</v>
+        <v>3477828497.775</v>
       </c>
       <c r="N12">
-        <v>3838779392.159</v>
+        <v>3845295311.175</v>
       </c>
     </row>
     <row r="13">
@@ -966,40 +966,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>41173.22</v>
+        <v>41290.246</v>
       </c>
       <c r="D13">
-        <v>39193.46</v>
+        <v>39300.321</v>
       </c>
       <c r="E13">
-        <v>43155.502</v>
+        <v>43277.956</v>
       </c>
       <c r="F13">
-        <v>48431.268</v>
+        <v>48539.728</v>
       </c>
       <c r="G13">
-        <v>46081.857</v>
+        <v>46179.685</v>
       </c>
       <c r="H13">
-        <v>50793.264</v>
+        <v>50916.821</v>
       </c>
       <c r="I13">
-        <v>2293706284.598</v>
+        <v>2300182584.386</v>
       </c>
       <c r="J13">
-        <v>2183774156.659</v>
+        <v>2189819743.318</v>
       </c>
       <c r="K13">
-        <v>2404043905.9</v>
+        <v>2411211199.576</v>
       </c>
       <c r="L13">
-        <v>6441560046.44</v>
+        <v>6455627367.512</v>
       </c>
       <c r="M13">
-        <v>6128411505.812</v>
+        <v>6141960436.63</v>
       </c>
       <c r="N13">
-        <v>6756403146.166</v>
+        <v>6771460756.993</v>
       </c>
     </row>
     <row r="14">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="C14">
-        <v>45945.706</v>
+        <v>45928.541</v>
       </c>
       <c r="D14">
-        <v>43558.955</v>
+        <v>43536.102</v>
       </c>
       <c r="E14">
-        <v>48337.86</v>
+        <v>48327.27</v>
       </c>
       <c r="F14">
-        <v>26408.646</v>
+        <v>26367.06</v>
       </c>
       <c r="G14">
-        <v>24983.327</v>
+        <v>24939.092</v>
       </c>
       <c r="H14">
-        <v>27856.571</v>
+        <v>27814.67</v>
       </c>
       <c r="I14">
-        <v>2559381454.864</v>
+        <v>2558540639.087</v>
       </c>
       <c r="J14">
-        <v>2426703719.529</v>
+        <v>2425285027.253</v>
       </c>
       <c r="K14">
-        <v>2692751888.989</v>
+        <v>2691690774.447</v>
       </c>
       <c r="L14">
-        <v>3511910990.48</v>
+        <v>3506636825.198</v>
       </c>
       <c r="M14">
-        <v>3321597679.6</v>
+        <v>3316030589.139</v>
       </c>
       <c r="N14">
-        <v>3703856471.658</v>
+        <v>3698402111.104</v>
       </c>
     </row>
     <row r="15">
@@ -1062,40 +1062,40 @@
         </is>
       </c>
       <c r="C15">
-        <v>33837.491</v>
+        <v>33850.838</v>
       </c>
       <c r="D15">
-        <v>31302.154</v>
+        <v>31309.113</v>
       </c>
       <c r="E15">
-        <v>36396.058</v>
+        <v>36409.141</v>
       </c>
       <c r="F15">
-        <v>2830.577</v>
+        <v>2818.782</v>
       </c>
       <c r="G15">
-        <v>2481.1</v>
+        <v>2470.848</v>
       </c>
       <c r="H15">
-        <v>3186.689</v>
+        <v>3172.684</v>
       </c>
       <c r="I15">
-        <v>1885113582.665</v>
+        <v>1885676121.504</v>
       </c>
       <c r="J15">
-        <v>1744029385.183</v>
+        <v>1744235384.975</v>
       </c>
       <c r="K15">
-        <v>2026857753.225</v>
+        <v>2028168341.544</v>
       </c>
       <c r="L15">
-        <v>376398888.036</v>
+        <v>374840831.763</v>
       </c>
       <c r="M15">
-        <v>329834457.642</v>
+        <v>328457947.822</v>
       </c>
       <c r="N15">
-        <v>423713274.685</v>
+        <v>421661057.995</v>
       </c>
     </row>
     <row r="16">
@@ -1110,40 +1110,40 @@
         </is>
       </c>
       <c r="C16">
-        <v>7356.744</v>
+        <v>7352.697</v>
       </c>
       <c r="D16">
-        <v>6674.648</v>
+        <v>6668.488</v>
       </c>
       <c r="E16">
-        <v>8071.579</v>
+        <v>8067.191</v>
       </c>
       <c r="F16">
-        <v>24862.012</v>
+        <v>24851.183</v>
       </c>
       <c r="G16">
-        <v>22473.823</v>
+        <v>22464.316</v>
       </c>
       <c r="H16">
-        <v>27355.944</v>
+        <v>27363.277</v>
       </c>
       <c r="I16">
-        <v>108912045.711</v>
+        <v>108848026.842</v>
       </c>
       <c r="J16">
-        <v>98760032.22499999</v>
+        <v>98752210.441</v>
       </c>
       <c r="K16">
-        <v>119471959.849</v>
+        <v>119394344.012</v>
       </c>
       <c r="L16">
-        <v>3306336738.954</v>
+        <v>3304767583.304</v>
       </c>
       <c r="M16">
-        <v>2990192964.912</v>
+        <v>2990942055.291</v>
       </c>
       <c r="N16">
-        <v>3640774335.282</v>
+        <v>3639848230.823</v>
       </c>
     </row>
     <row r="17">
@@ -1158,40 +1158,40 @@
         </is>
       </c>
       <c r="C17">
-        <v>12674.197</v>
+        <v>12788.501</v>
       </c>
       <c r="D17">
-        <v>11624.356</v>
+        <v>11731.411</v>
       </c>
       <c r="E17">
-        <v>13765.19</v>
+        <v>13880.821</v>
       </c>
       <c r="F17">
-        <v>35386.326</v>
+        <v>35734.04</v>
       </c>
       <c r="G17">
-        <v>32387.089</v>
+        <v>32710.28</v>
       </c>
       <c r="H17">
-        <v>38514.375</v>
+        <v>38884.753</v>
       </c>
       <c r="I17">
-        <v>187705241.03</v>
+        <v>189366630.336</v>
       </c>
       <c r="J17">
-        <v>172149234.687</v>
+        <v>173697666.594</v>
       </c>
       <c r="K17">
-        <v>203817419.224</v>
+        <v>205642672.498</v>
       </c>
       <c r="L17">
-        <v>4706262707.251</v>
+        <v>4753480551.743</v>
       </c>
       <c r="M17">
-        <v>4307088946.599</v>
+        <v>4350951181.105</v>
       </c>
       <c r="N17">
-        <v>5123140442.356</v>
+        <v>5172607832.056</v>
       </c>
     </row>
     <row r="18">
@@ -1206,40 +1206,40 @@
         </is>
       </c>
       <c r="C18">
-        <v>20456.292</v>
+        <v>20509.025</v>
       </c>
       <c r="D18">
-        <v>18907.85</v>
+        <v>18961.283</v>
       </c>
       <c r="E18">
-        <v>22067.217</v>
+        <v>22107.236</v>
       </c>
       <c r="F18">
-        <v>45895.495</v>
+        <v>46008.567</v>
       </c>
       <c r="G18">
-        <v>42214.713</v>
+        <v>42363.117</v>
       </c>
       <c r="H18">
-        <v>49738.33</v>
+        <v>49804.151</v>
       </c>
       <c r="I18">
-        <v>302933283.722</v>
+        <v>303689769.066</v>
       </c>
       <c r="J18">
-        <v>279831711.853</v>
+        <v>280664695.324</v>
       </c>
       <c r="K18">
-        <v>326858508.899</v>
+        <v>327402290.839</v>
       </c>
       <c r="L18">
-        <v>6104016858.043</v>
+        <v>6118924337.99</v>
       </c>
       <c r="M18">
-        <v>5616250935.726</v>
+        <v>5632035020.269</v>
       </c>
       <c r="N18">
-        <v>6613202070.441</v>
+        <v>6621656436.896</v>
       </c>
     </row>
     <row r="19">
@@ -1254,40 +1254,40 @@
         </is>
       </c>
       <c r="C19">
-        <v>25576.792</v>
+        <v>25621.114</v>
       </c>
       <c r="D19">
-        <v>23997.998</v>
+        <v>24064.608</v>
       </c>
       <c r="E19">
-        <v>27187.368</v>
+        <v>27227.942</v>
       </c>
       <c r="F19">
-        <v>41872.863</v>
+        <v>41933.988</v>
       </c>
       <c r="G19">
-        <v>39187.944</v>
+        <v>39261.794</v>
       </c>
       <c r="H19">
-        <v>44642.129</v>
+        <v>44708.428</v>
       </c>
       <c r="I19">
-        <v>378804478.967</v>
+        <v>379434069.707</v>
       </c>
       <c r="J19">
-        <v>355519623.004</v>
+        <v>356406598.93</v>
       </c>
       <c r="K19">
-        <v>402461547.026</v>
+        <v>403278363.437</v>
       </c>
       <c r="L19">
-        <v>5568377481.985</v>
+        <v>5577328060.208</v>
       </c>
       <c r="M19">
-        <v>5211420191.578</v>
+        <v>5223932716.844</v>
       </c>
       <c r="N19">
-        <v>5935989240.415</v>
+        <v>5946155718.272</v>
       </c>
     </row>
     <row r="20">
@@ -1302,40 +1302,40 @@
         </is>
       </c>
       <c r="C20">
-        <v>32472.697</v>
+        <v>32382.16</v>
       </c>
       <c r="D20">
-        <v>30712.188</v>
+        <v>30606.807</v>
       </c>
       <c r="E20">
-        <v>34272.808</v>
+        <v>34200.551</v>
       </c>
       <c r="F20">
-        <v>34280.983</v>
+        <v>34168.184</v>
       </c>
       <c r="G20">
-        <v>32323.696</v>
+        <v>32193.915</v>
       </c>
       <c r="H20">
-        <v>36282.339</v>
+        <v>36201.136</v>
       </c>
       <c r="I20">
-        <v>480811246.019</v>
+        <v>479461233.66</v>
       </c>
       <c r="J20">
-        <v>454660868.112</v>
+        <v>453132672.56</v>
       </c>
       <c r="K20">
-        <v>507588226.984</v>
+        <v>506533807.393</v>
       </c>
       <c r="L20">
-        <v>4559192162.931</v>
+        <v>4544495366.256</v>
       </c>
       <c r="M20">
-        <v>4299256463.701</v>
+        <v>4282831906.929</v>
       </c>
       <c r="N20">
-        <v>4826304936.02</v>
+        <v>4814629557.991</v>
       </c>
     </row>
     <row r="21">
@@ -1350,40 +1350,40 @@
         </is>
       </c>
       <c r="C21">
-        <v>21608.455</v>
+        <v>21574.217</v>
       </c>
       <c r="D21">
-        <v>20260.965</v>
+        <v>20231.77</v>
       </c>
       <c r="E21">
-        <v>22987.722</v>
+        <v>22949.178</v>
       </c>
       <c r="F21">
-        <v>10684.4</v>
+        <v>10655.435</v>
       </c>
       <c r="G21">
-        <v>9982.754999999999</v>
+        <v>9957.656000000001</v>
       </c>
       <c r="H21">
-        <v>11394.92</v>
+        <v>11372.823</v>
       </c>
       <c r="I21">
-        <v>319957370.023</v>
+        <v>319457481.855</v>
       </c>
       <c r="J21">
-        <v>299990462.805</v>
+        <v>299470475.577</v>
       </c>
       <c r="K21">
-        <v>340352667.26</v>
+        <v>339803447.001</v>
       </c>
       <c r="L21">
-        <v>1420519258.408</v>
+        <v>1417091211.804</v>
       </c>
       <c r="M21">
-        <v>1328247475.99</v>
+        <v>1324309638.588</v>
       </c>
       <c r="N21">
-        <v>1516028432.354</v>
+        <v>1512439299.512</v>
       </c>
     </row>
     <row r="22">
@@ -1398,40 +1398,40 @@
         </is>
       </c>
       <c r="C22">
-        <v>9913.777</v>
+        <v>9908.245999999999</v>
       </c>
       <c r="D22">
-        <v>8997.022999999999</v>
+        <v>8990.181</v>
       </c>
       <c r="E22">
-        <v>10860.781</v>
+        <v>10855.247</v>
       </c>
       <c r="F22">
-        <v>636.2670000000001</v>
+        <v>636.212</v>
       </c>
       <c r="G22">
-        <v>543.438</v>
+        <v>543.491</v>
       </c>
       <c r="H22">
-        <v>734.047</v>
+        <v>733.068</v>
       </c>
       <c r="I22">
-        <v>146765311.842</v>
+        <v>146686360.694</v>
       </c>
       <c r="J22">
-        <v>133223813.761</v>
+        <v>133072279.127</v>
       </c>
       <c r="K22">
-        <v>160828739.697</v>
+        <v>160720969.652</v>
       </c>
       <c r="L22">
-        <v>84658377.751</v>
+        <v>84606083.479</v>
       </c>
       <c r="M22">
-        <v>72218518.23199999</v>
+        <v>72230635.984</v>
       </c>
       <c r="N22">
-        <v>97553797.32700001</v>
+        <v>97519017.271</v>
       </c>
     </row>
     <row r="23">
@@ -1446,40 +1446,40 @@
         </is>
       </c>
       <c r="C23">
-        <v>1561.824</v>
+        <v>1567.521</v>
       </c>
       <c r="D23">
-        <v>1434.319</v>
+        <v>1439.194</v>
       </c>
       <c r="E23">
-        <v>1692.828</v>
+        <v>1700.565</v>
       </c>
       <c r="F23">
-        <v>6308.635</v>
+        <v>6328.622</v>
       </c>
       <c r="G23">
-        <v>5790.324</v>
+        <v>5801.345</v>
       </c>
       <c r="H23">
-        <v>6848.198</v>
+        <v>6871.62</v>
       </c>
       <c r="I23">
-        <v>117399703.275</v>
+        <v>117848007.426</v>
       </c>
       <c r="J23">
-        <v>107913292.576</v>
+        <v>108227536.304</v>
       </c>
       <c r="K23">
-        <v>127298765.503</v>
+        <v>127867837.337</v>
       </c>
       <c r="L23">
-        <v>839057931.222</v>
+        <v>841717666.686</v>
       </c>
       <c r="M23">
-        <v>769806404.878</v>
+        <v>771895862.001</v>
       </c>
       <c r="N23">
-        <v>911324463.498</v>
+        <v>914543061.0930001</v>
       </c>
     </row>
     <row r="24">
@@ -1494,40 +1494,40 @@
         </is>
       </c>
       <c r="C24">
-        <v>2863.213</v>
+        <v>2835.075</v>
       </c>
       <c r="D24">
-        <v>2656.139</v>
+        <v>2632.214</v>
       </c>
       <c r="E24">
-        <v>3074.34</v>
+        <v>3042.39</v>
       </c>
       <c r="F24">
-        <v>9376.754000000001</v>
+        <v>9280.495000000001</v>
       </c>
       <c r="G24">
-        <v>8704.67</v>
+        <v>8620.054</v>
       </c>
       <c r="H24">
-        <v>10068.825</v>
+        <v>9958.044</v>
       </c>
       <c r="I24">
-        <v>215339421.419</v>
+        <v>213234815.476</v>
       </c>
       <c r="J24">
-        <v>199826230.686</v>
+        <v>198073565.851</v>
       </c>
       <c r="K24">
-        <v>231134244.395</v>
+        <v>228737472.533</v>
       </c>
       <c r="L24">
-        <v>1247489329.061</v>
+        <v>1234739358.601</v>
       </c>
       <c r="M24">
-        <v>1158078143.435</v>
+        <v>1146698055.839</v>
       </c>
       <c r="N24">
-        <v>1339525593.784</v>
+        <v>1324835130.263</v>
       </c>
     </row>
     <row r="25">
@@ -1542,40 +1542,40 @@
         </is>
       </c>
       <c r="C25">
-        <v>4850.94</v>
+        <v>4850.269</v>
       </c>
       <c r="D25">
-        <v>4503.862</v>
+        <v>4503.636</v>
       </c>
       <c r="E25">
-        <v>5207.689</v>
+        <v>5206.447</v>
       </c>
       <c r="F25">
-        <v>12614.391</v>
+        <v>12612.319</v>
       </c>
       <c r="G25">
-        <v>11710.612</v>
+        <v>11708.303</v>
       </c>
       <c r="H25">
-        <v>13540.85</v>
+        <v>13542.168</v>
       </c>
       <c r="I25">
-        <v>364754171.078</v>
+        <v>364730026.928</v>
       </c>
       <c r="J25">
-        <v>338811335.668</v>
+        <v>338837135.953</v>
       </c>
       <c r="K25">
-        <v>391675284.363</v>
+        <v>391525708.262</v>
       </c>
       <c r="L25">
-        <v>1677743523.899</v>
+        <v>1677240151.008</v>
       </c>
       <c r="M25">
-        <v>1557109859.276</v>
+        <v>1557072004.269</v>
       </c>
       <c r="N25">
-        <v>1801043043.906</v>
+        <v>1801564628.428</v>
       </c>
     </row>
     <row r="26">
@@ -1590,40 +1590,40 @@
         </is>
       </c>
       <c r="C26">
-        <v>7108.913</v>
+        <v>7113.08</v>
       </c>
       <c r="D26">
-        <v>6699.913</v>
+        <v>6703.379</v>
       </c>
       <c r="E26">
-        <v>7527.046</v>
+        <v>7532.607</v>
       </c>
       <c r="F26">
-        <v>13680.996</v>
+        <v>13696.07</v>
       </c>
       <c r="G26">
-        <v>12893.101</v>
+        <v>12902.681</v>
       </c>
       <c r="H26">
-        <v>14484.157</v>
+        <v>14505.745</v>
       </c>
       <c r="I26">
-        <v>534648215.123</v>
+        <v>534898043.887</v>
       </c>
       <c r="J26">
-        <v>503847728.532</v>
+        <v>504242646.643</v>
       </c>
       <c r="K26">
-        <v>566013518.011</v>
+        <v>566498834.7079999</v>
       </c>
       <c r="L26">
-        <v>1819974702.833</v>
+        <v>1821887243.811</v>
       </c>
       <c r="M26">
-        <v>1715441783.876</v>
+        <v>1716959198.264</v>
       </c>
       <c r="N26">
-        <v>1927022484.359</v>
+        <v>1929566195.465</v>
       </c>
     </row>
     <row r="27">
@@ -1638,40 +1638,40 @@
         </is>
       </c>
       <c r="C27">
-        <v>8520.771000000001</v>
+        <v>8542.942999999999</v>
       </c>
       <c r="D27">
-        <v>8062.959</v>
+        <v>8083.973</v>
       </c>
       <c r="E27">
-        <v>8988.798000000001</v>
+        <v>9014.67</v>
       </c>
       <c r="F27">
-        <v>10934.597</v>
+        <v>10975.667</v>
       </c>
       <c r="G27">
-        <v>10330.463</v>
+        <v>10364.158</v>
       </c>
       <c r="H27">
-        <v>11559.326</v>
+        <v>11608.113</v>
       </c>
       <c r="I27">
-        <v>640647981.59</v>
+        <v>642405025.7690001</v>
       </c>
       <c r="J27">
-        <v>606398367.84</v>
+        <v>607852699.727</v>
       </c>
       <c r="K27">
-        <v>675705992.719</v>
+        <v>677737484.0089999</v>
       </c>
       <c r="L27">
-        <v>1454829519.7</v>
+        <v>1460387436.91</v>
       </c>
       <c r="M27">
-        <v>1374244459.217</v>
+        <v>1378764715.492</v>
       </c>
       <c r="N27">
-        <v>1537020241.781</v>
+        <v>1543401545.5</v>
       </c>
     </row>
     <row r="28">
@@ -1686,40 +1686,40 @@
         </is>
       </c>
       <c r="C28">
-        <v>2719.686</v>
+        <v>2734.138</v>
       </c>
       <c r="D28">
-        <v>2554.523</v>
+        <v>2568.229</v>
       </c>
       <c r="E28">
-        <v>2887.511</v>
+        <v>2902.838</v>
       </c>
       <c r="F28">
-        <v>1744.579</v>
+        <v>1756.715</v>
       </c>
       <c r="G28">
-        <v>1629.441</v>
+        <v>1640.464</v>
       </c>
       <c r="H28">
-        <v>1861.324</v>
+        <v>1875.356</v>
       </c>
       <c r="I28">
-        <v>204493687.004</v>
+        <v>205591412.935</v>
       </c>
       <c r="J28">
-        <v>192082769.382</v>
+        <v>193138989.874</v>
       </c>
       <c r="K28">
-        <v>217114066.29</v>
+        <v>218294943.42</v>
       </c>
       <c r="L28">
-        <v>231972695.858</v>
+        <v>233600083.842</v>
       </c>
       <c r="M28">
-        <v>216718189.669</v>
+        <v>218069306.666</v>
       </c>
       <c r="N28">
-        <v>247541934.038</v>
+        <v>249420658.776</v>
       </c>
     </row>
     <row r="29">
@@ -1734,40 +1734,40 @@
         </is>
       </c>
       <c r="C29">
-        <v>127.711</v>
+        <v>126.422</v>
       </c>
       <c r="D29">
-        <v>116.278</v>
+        <v>115.161</v>
       </c>
       <c r="E29">
-        <v>139.427</v>
+        <v>138.179</v>
       </c>
       <c r="F29">
-        <v>13.852</v>
+        <v>13.66</v>
       </c>
       <c r="G29">
-        <v>11.825</v>
+        <v>11.663</v>
       </c>
       <c r="H29">
-        <v>16.002</v>
+        <v>15.807</v>
       </c>
       <c r="I29">
-        <v>9605759.187000001</v>
+        <v>9506232.438999999</v>
       </c>
       <c r="J29">
-        <v>8743882.581</v>
+        <v>8667344.334000001</v>
       </c>
       <c r="K29">
-        <v>10484675.886</v>
+        <v>10388700.399</v>
       </c>
       <c r="L29">
-        <v>1842694.42</v>
+        <v>1817055.217</v>
       </c>
       <c r="M29">
-        <v>1572287.463</v>
+        <v>1550818.051</v>
       </c>
       <c r="N29">
-        <v>2128922.532</v>
+        <v>2104404.498</v>
       </c>
     </row>
     <row r="30">
@@ -1878,40 +1878,40 @@
         </is>
       </c>
       <c r="C32">
-        <v>676.491</v>
+        <v>685.878</v>
       </c>
       <c r="D32">
-        <v>636.6799999999999</v>
+        <v>645.664</v>
       </c>
       <c r="E32">
-        <v>716.929</v>
+        <v>726.61</v>
       </c>
       <c r="F32">
-        <v>5426.342</v>
+        <v>5502.186</v>
       </c>
       <c r="G32">
-        <v>5098.838</v>
+        <v>5170.708</v>
       </c>
       <c r="H32">
-        <v>5758.524</v>
+        <v>5837.987</v>
       </c>
       <c r="I32">
-        <v>11391658.729</v>
+        <v>11549408.832</v>
       </c>
       <c r="J32">
-        <v>10719689.694</v>
+        <v>10871613.747</v>
       </c>
       <c r="K32">
-        <v>12072276.568</v>
+        <v>12236684.256</v>
       </c>
       <c r="L32">
-        <v>721674206.064</v>
+        <v>731758377.8430001</v>
       </c>
       <c r="M32">
-        <v>678134054.4119999</v>
+        <v>687706137.446</v>
       </c>
       <c r="N32">
-        <v>766230804.988</v>
+        <v>776732292.918</v>
       </c>
     </row>
     <row r="33">
@@ -1926,40 +1926,40 @@
         </is>
       </c>
       <c r="C33">
-        <v>1276.87</v>
+        <v>1255.175</v>
       </c>
       <c r="D33">
-        <v>1213.403</v>
+        <v>1192.876</v>
       </c>
       <c r="E33">
-        <v>1341.274</v>
+        <v>1318.36</v>
       </c>
       <c r="F33">
-        <v>7547.567</v>
+        <v>7412.736</v>
       </c>
       <c r="G33">
-        <v>7160.019</v>
+        <v>7037.172</v>
       </c>
       <c r="H33">
-        <v>7937.118</v>
+        <v>7794.636</v>
       </c>
       <c r="I33">
-        <v>21500124.081</v>
+        <v>21136648.636</v>
       </c>
       <c r="J33">
-        <v>20431212.74</v>
+        <v>20085749.864</v>
       </c>
       <c r="K33">
-        <v>22581067.143</v>
+        <v>22195381.019</v>
       </c>
       <c r="L33">
-        <v>1003797961.581</v>
+        <v>985958726.145</v>
       </c>
       <c r="M33">
-        <v>952515542.965</v>
+        <v>936051418.516</v>
       </c>
       <c r="N33">
-        <v>1055724780.889</v>
+        <v>1036672479.633</v>
       </c>
     </row>
     <row r="34">
@@ -1974,40 +1974,40 @@
         </is>
       </c>
       <c r="C34">
-        <v>6783.272</v>
+        <v>6819.58</v>
       </c>
       <c r="D34">
-        <v>6478.184</v>
+        <v>6512.267</v>
       </c>
       <c r="E34">
-        <v>7091.214</v>
+        <v>7128.336</v>
       </c>
       <c r="F34">
-        <v>26463.087</v>
+        <v>26618.414</v>
       </c>
       <c r="G34">
-        <v>25214.948</v>
+        <v>25358.583</v>
       </c>
       <c r="H34">
-        <v>27719.369</v>
+        <v>27882.657</v>
       </c>
       <c r="I34">
-        <v>114223000.836</v>
+        <v>114843091.676</v>
       </c>
       <c r="J34">
-        <v>109082924.406</v>
+        <v>109660138.058</v>
       </c>
       <c r="K34">
-        <v>119434975.677</v>
+        <v>120064348.003</v>
       </c>
       <c r="L34">
-        <v>3519719552.039</v>
+        <v>3540132170.937</v>
       </c>
       <c r="M34">
-        <v>3352504195.13</v>
+        <v>3372298356.312</v>
       </c>
       <c r="N34">
-        <v>3687121572.936</v>
+        <v>3709424249.948</v>
       </c>
     </row>
     <row r="35">
@@ -2022,40 +2022,40 @@
         </is>
       </c>
       <c r="C35">
-        <v>17619.06</v>
+        <v>17611.344</v>
       </c>
       <c r="D35">
-        <v>16734.343</v>
+        <v>16729.15</v>
       </c>
       <c r="E35">
-        <v>18514.401</v>
+        <v>18499.753</v>
       </c>
       <c r="F35">
-        <v>34670.279</v>
+        <v>34612.491</v>
       </c>
       <c r="G35">
-        <v>32716.3</v>
+        <v>32673.861</v>
       </c>
       <c r="H35">
-        <v>36631.019</v>
+        <v>36559.749</v>
       </c>
       <c r="I35">
-        <v>296731397.468</v>
+        <v>296613159.171</v>
       </c>
       <c r="J35">
-        <v>281846474.356</v>
+        <v>281736511.717</v>
       </c>
       <c r="K35">
-        <v>311752898.834</v>
+        <v>311550483.726</v>
       </c>
       <c r="L35">
-        <v>4611464625.568</v>
+        <v>4604240072.138</v>
       </c>
       <c r="M35">
-        <v>4351728207.734</v>
+        <v>4345282684.393</v>
       </c>
       <c r="N35">
-        <v>4870683539.127</v>
+        <v>4861200316.424</v>
       </c>
     </row>
     <row r="36">
@@ -2070,40 +2070,40 @@
         </is>
       </c>
       <c r="C36">
-        <v>24708.613</v>
+        <v>24687.122</v>
       </c>
       <c r="D36">
-        <v>22908.332</v>
+        <v>22895.249</v>
       </c>
       <c r="E36">
-        <v>26525.068</v>
+        <v>26499.973</v>
       </c>
       <c r="F36">
-        <v>7637.004</v>
+        <v>7647.949</v>
       </c>
       <c r="G36">
-        <v>6703.806</v>
+        <v>6714.014</v>
       </c>
       <c r="H36">
-        <v>8576.359</v>
+        <v>8588.148999999999</v>
       </c>
       <c r="I36">
-        <v>416197756.975</v>
+        <v>415817885.446</v>
       </c>
       <c r="J36">
-        <v>385780114.177</v>
+        <v>385475752.123</v>
       </c>
       <c r="K36">
-        <v>446756775.873</v>
+        <v>446299830.818</v>
       </c>
       <c r="L36">
-        <v>1015518894.718</v>
+        <v>1016912845.068</v>
       </c>
       <c r="M36">
-        <v>891544177.074</v>
+        <v>892930179.418</v>
       </c>
       <c r="N36">
-        <v>1141510335.528</v>
+        <v>1142805798.196</v>
       </c>
     </row>
     <row r="37">
@@ -2118,22 +2118,22 @@
         </is>
       </c>
       <c r="C37">
-        <v>87300.429</v>
+        <v>70724.276</v>
       </c>
       <c r="D37">
-        <v>81353.496</v>
+        <v>65689.397</v>
       </c>
       <c r="E37">
-        <v>93308.087</v>
+        <v>75887.41499999999</v>
       </c>
       <c r="F37">
-        <v>455884.607</v>
+        <v>39950.362</v>
       </c>
       <c r="G37">
-        <v>422409.309</v>
+        <v>36888.031</v>
       </c>
       <c r="H37">
-        <v>489886.922</v>
+        <v>43098.095</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2145,13 +2145,13 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>60633331851.077</v>
+        <v>5312680305.951</v>
       </c>
       <c r="M37">
-        <v>56208330178.727</v>
+        <v>4909407868.156</v>
       </c>
       <c r="N37">
-        <v>65163297458.354</v>
+        <v>5733688185.568</v>
       </c>
     </row>
     <row r="38">
@@ -2166,22 +2166,22 @@
         </is>
       </c>
       <c r="C38">
-        <v>98666.829</v>
+        <v>80422.93799999999</v>
       </c>
       <c r="D38">
-        <v>92771.77800000001</v>
+        <v>75381.71799999999</v>
       </c>
       <c r="E38">
-        <v>104582.667</v>
+        <v>85544.181</v>
       </c>
       <c r="F38">
-        <v>423830.336</v>
+        <v>37866.327</v>
       </c>
       <c r="G38">
-        <v>396684.375</v>
+        <v>35350.33</v>
       </c>
       <c r="H38">
-        <v>451396.471</v>
+        <v>40441.472</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2193,13 +2193,13 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>56362249815.286</v>
+        <v>5035482298.574</v>
       </c>
       <c r="M38">
-        <v>52761692192.667</v>
+        <v>4700969878.751</v>
       </c>
       <c r="N38">
-        <v>60014249345.76</v>
+        <v>5378299751.578</v>
       </c>
     </row>
     <row r="39">
@@ -2214,22 +2214,22 @@
         </is>
       </c>
       <c r="C39">
-        <v>111731.587</v>
+        <v>92174.24800000001</v>
       </c>
       <c r="D39">
-        <v>105382.27</v>
+        <v>86707.242</v>
       </c>
       <c r="E39">
-        <v>118113.814</v>
+        <v>97706.401</v>
       </c>
       <c r="F39">
-        <v>386142.137</v>
+        <v>35879.772</v>
       </c>
       <c r="G39">
-        <v>362077.974</v>
+        <v>33555.925</v>
       </c>
       <c r="H39">
-        <v>410635.25</v>
+        <v>38253.115</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2241,13 +2241,13 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>51355009491.417</v>
+        <v>4771537315.121</v>
       </c>
       <c r="M39">
-        <v>48163934773.157</v>
+        <v>4463897171.493</v>
       </c>
       <c r="N39">
-        <v>54601190178.686</v>
+        <v>5087596164.28</v>
       </c>
     </row>
     <row r="40">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="C40">
-        <v>102686.81</v>
+        <v>85864.12</v>
       </c>
       <c r="D40">
-        <v>97668.73699999999</v>
+        <v>81506.564</v>
       </c>
       <c r="E40">
-        <v>107721.82</v>
+        <v>90279.197</v>
       </c>
       <c r="F40">
-        <v>263297.68</v>
+        <v>25502.629</v>
       </c>
       <c r="G40">
-        <v>249264.705</v>
+        <v>24092.157</v>
       </c>
       <c r="H40">
-        <v>277530.023</v>
+        <v>26940.337</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2289,13 +2289,13 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>35018140074.305</v>
+        <v>3392092370.755</v>
       </c>
       <c r="M40">
-        <v>33149236392.199</v>
+        <v>3203322144.206</v>
       </c>
       <c r="N40">
-        <v>36918198120.476</v>
+        <v>3583197320.783</v>
       </c>
     </row>
     <row r="41">
@@ -2310,22 +2310,22 @@
         </is>
       </c>
       <c r="C41">
-        <v>108140.564</v>
+        <v>90639.17200000001</v>
       </c>
       <c r="D41">
-        <v>103237.965</v>
+        <v>86368.946</v>
       </c>
       <c r="E41">
-        <v>113042.915</v>
+        <v>94927.213</v>
       </c>
       <c r="F41">
-        <v>186618.72</v>
+        <v>18380.476</v>
       </c>
       <c r="G41">
-        <v>177069.584</v>
+        <v>17407.909</v>
       </c>
       <c r="H41">
-        <v>196303.167</v>
+        <v>19373.698</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2337,13 +2337,13 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>24819115786.839</v>
+        <v>2444539844.873</v>
       </c>
       <c r="M41">
-        <v>23549864575.982</v>
+        <v>2314452972.936</v>
       </c>
       <c r="N41">
-        <v>26099604945.394</v>
+        <v>2575843830.597</v>
       </c>
     </row>
     <row r="42">
@@ -2358,22 +2358,22 @@
         </is>
       </c>
       <c r="C42">
-        <v>71784.21400000001</v>
+        <v>60379.554</v>
       </c>
       <c r="D42">
-        <v>68098.825</v>
+        <v>57186.366</v>
       </c>
       <c r="E42">
-        <v>75489.16499999999</v>
+        <v>63615.236</v>
       </c>
       <c r="F42">
-        <v>64327.286</v>
+        <v>6463.39</v>
       </c>
       <c r="G42">
-        <v>60390.498</v>
+        <v>6053.589</v>
       </c>
       <c r="H42">
-        <v>68339.149</v>
+        <v>6879.138</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2385,13 +2385,13 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>8556205973.624</v>
+        <v>859662914.285</v>
       </c>
       <c r="M42">
-        <v>8032519967.672</v>
+        <v>805466614.773</v>
       </c>
       <c r="N42">
-        <v>9084176466.278</v>
+        <v>914916865.752</v>
       </c>
     </row>
     <row r="43">
@@ -2406,22 +2406,22 @@
         </is>
       </c>
       <c r="C43">
-        <v>36348.701</v>
+        <v>31338.3</v>
       </c>
       <c r="D43">
-        <v>33670.425</v>
+        <v>28971.958</v>
       </c>
       <c r="E43">
-        <v>39034.403</v>
+        <v>33728.6</v>
       </c>
       <c r="F43">
-        <v>5692.825</v>
+        <v>615.276</v>
       </c>
       <c r="G43">
-        <v>4979.238</v>
+        <v>536.67</v>
       </c>
       <c r="H43">
-        <v>6428.486</v>
+        <v>696.524</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2433,13 +2433,13 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>757007593.567</v>
+        <v>81819375.76100001</v>
       </c>
       <c r="M43">
-        <v>662130597.503</v>
+        <v>71322092.167</v>
       </c>
       <c r="N43">
-        <v>854512276.5779999</v>
+        <v>92619484.685</v>
       </c>
     </row>
   </sheetData>
